--- a/봉제현황/생산평균_주간비교_월토_20261007.xlsx
+++ b/봉제현황/생산평균_주간비교_월토_20261007.xlsx
@@ -652,6 +652,9 @@
       <c r="E7" t="n">
         <v>240</v>
       </c>
+      <c r="F7" t="n">
+        <v>240</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -749,12 +752,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>판독보류</t>
-        </is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>240</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/7(수) 애리후세 판독불확실 240/230 (가운데 자리 덧씀) → null · 조업은 함 · 확인 후 집계 반영</t>
+          <t>10/7(수) 애리후세 240 · 사용자 확정 2026-10-07 18:30 (가운데 자리 덧씀 240/230)</t>
         </is>
       </c>
     </row>
@@ -828,7 +834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2/5 조업 (월 10/5 휴무 제외) · 집계 1일, 판독보류 1일(10/7)</t>
+          <t>2/5 조업 (월 10/5 휴무 제외)</t>
         </is>
       </c>
     </row>
@@ -859,12 +865,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>판독보류</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10/7(수) 애리후세 240/230 → null, 집계 제외</t>
+          <t>10/7(수) 애리후세 240 · 사용자 확정 2026-10-07 18:30 (판독 240/230)</t>
         </is>
       </c>
     </row>

--- a/봉제현황/생산평균_주간비교_월토_20261007.xlsx
+++ b/봉제현황/생산평균_주간비교_월토_20261007.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>240</v>
       </c>
       <c r="F7" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/7(수) 애리후세 240 · 사용자 확정 2026-10-07 18:30 (가운데 자리 덧씀 240/230)</t>
+          <t>10/7(수) 애리후세 280 · 사용자 확정 2026-10-07 18:38 280 (18:30 240 정정)</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10/7(수) 애리후세 240 · 사용자 확정 2026-10-07 18:30 (판독 240/230)</t>
+          <t>10/7(수) 애리후세 280 · 사용자 확정 2026-10-07 18:38 280 (18:30 240 정정) (판독 240/230)</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-324.7</v>
+        <v>-304.7</v>
       </c>
     </row>
     <row r="6">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-278.3</v>
+        <v>-258.3</v>
       </c>
     </row>
   </sheetData>
